--- a/data/trans_orig/Q5417-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q5417-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6552</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6381</t>
+          <t>6357</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6389</t>
+          <t>5811</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6671</t>
+          <t>6089</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16049</t>
+          <t>15573</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5542</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18306</t>
+          <t>19295</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>285336</t>
+          <t>285276</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>291778</t>
+          <t>291786</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>323305</t>
+          <t>324090</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>336582</t>
+          <t>336301</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>612375</t>
+          <t>611690</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>627377</t>
+          <t>627730</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9226</t>
+          <t>9127</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9672</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9893</t>
+          <t>10501</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11610</t>
+          <t>10878</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13976</t>
+          <t>14884</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7989</t>
+          <t>8519</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24798</t>
+          <t>25142</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14280</t>
+          <t>14911</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33039</t>
+          <t>33831</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>194173</t>
+          <t>192838</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>205371</t>
+          <t>205164</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>300546</t>
+          <t>300388</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>320965</t>
+          <t>319988</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>500282</t>
+          <t>499491</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>522939</t>
+          <t>521911</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11284</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11530</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>5905</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11822</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2934</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>14171</t>
+          <t>13642</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4855</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15871</t>
+          <t>16290</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15652</t>
+          <t>16660</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35321</t>
+          <t>37971</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23435</t>
+          <t>22421</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46665</t>
+          <t>45874</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>483452</t>
+          <t>482300</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>495829</t>
+          <t>495536</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>629853</t>
+          <t>630344</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>653390</t>
+          <t>652980</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1118150</t>
+          <t>1118670</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1144688</t>
+          <t>1145320</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9537</t>
+          <t>9690</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11079</t>
+          <t>12235</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6544</t>
+          <t>5969</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5952</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -2896,12 +2896,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9613</t>
+          <t>10420</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16681</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6878</t>
+          <t>7651</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21216</t>
+          <t>23195</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -2981,12 +2981,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>294070</t>
+          <t>294330</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>305735</t>
+          <t>305697</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>333898</t>
+          <t>334772</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>348982</t>
+          <t>348440</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>635409</t>
+          <t>633781</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>652421</t>
+          <t>651730</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8533</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6826</t>
+          <t>7188</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22729</t>
+          <t>23029</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>9011</t>
+          <t>9758</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>26628</t>
+          <t>26743</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16998</t>
+          <t>12080</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>7600</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22854</t>
+          <t>24114</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9902</t>
+          <t>9849</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29519</t>
+          <t>29280</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>18627</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18838</t>
+          <t>18788</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40316</t>
+          <t>41163</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28642</t>
+          <t>28939</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53678</t>
+          <t>53544</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>220249</t>
+          <t>220289</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>238999</t>
+          <t>239070</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>319365</t>
+          <t>316940</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>347912</t>
+          <t>346104</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>545001</t>
+          <t>546750</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>579943</t>
+          <t>581392</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>91,01%</t>
         </is>
       </c>
     </row>
@@ -3808,12 +3808,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14488</t>
+          <t>13701</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3843,12 +3843,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7870</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23695</t>
+          <t>24326</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14182</t>
+          <t>14171</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>33100</t>
+          <t>32616</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -3921,12 +3921,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13101</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6763</t>
+          <t>7458</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23083</t>
+          <t>23555</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3971,12 +3971,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>11675</t>
+          <t>9719</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>31978</t>
+          <t>29712</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -4034,12 +4034,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>8357</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24542</t>
+          <t>25706</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26889</t>
+          <t>25931</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50610</t>
+          <t>49849</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38076</t>
+          <t>39040</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>67312</t>
+          <t>66716</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>522689</t>
+          <t>520565</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>542791</t>
+          <t>541850</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>659558</t>
+          <t>661364</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>692067</t>
+          <t>692557</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1189090</t>
+          <t>1192444</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1227308</t>
+          <t>1228512</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,31%</t>
         </is>
       </c>
     </row>
@@ -4725,7 +4725,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>5809</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6826</t>
+          <t>5939</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7819</t>
+          <t>8809</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11580</t>
+          <t>11425</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14509</t>
+          <t>14003</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4918,12 +4918,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>325312</t>
+          <t>325101</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>364520</t>
+          <t>365262</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>375595</t>
+          <t>375699</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4996,12 +4996,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>695116</t>
+          <t>695470</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>708075</t>
+          <t>708123</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>881</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5191,12 +5191,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3973</t>
+          <t>3853</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18822</t>
+          <t>18593</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5226,12 +5226,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5906</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>21743</t>
+          <t>21842</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5261,12 +5261,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -5289,12 +5289,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2525</t>
+          <t>2519</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11836</t>
+          <t>11259</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>1177</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10766</t>
+          <t>9838</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5339,12 +5339,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17154</t>
+          <t>17627</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5374,12 +5374,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -5402,12 +5402,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14896</t>
+          <t>15548</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5417,12 +5417,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5437,12 +5437,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17295</t>
+          <t>17965</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39224</t>
+          <t>40520</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5452,12 +5452,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5472,12 +5472,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24710</t>
+          <t>24341</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51019</t>
+          <t>49126</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5487,12 +5487,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -5515,12 +5515,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>231162</t>
+          <t>230187</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>246053</t>
+          <t>245305</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>343192</t>
+          <t>343994</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>371555</t>
+          <t>372175</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5565,12 +5565,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>582281</t>
+          <t>584989</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>613352</t>
+          <t>613559</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5600,12 +5600,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,36%</t>
         </is>
       </c>
     </row>
@@ -5745,12 +5745,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7267</t>
+          <t>7194</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5765,34 +5765,34 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>9535</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3820</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>18432</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>1,23%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>9535</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>3776</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>19016</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,49%</t>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21437</t>
+          <t>21042</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -5858,12 +5858,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13088</t>
+          <t>13187</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11677</t>
+          <t>11067</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>6451</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>20266</t>
+          <t>19722</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -5971,12 +5971,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18163</t>
+          <t>18050</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5986,12 +5986,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21368</t>
+          <t>21372</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45813</t>
+          <t>47754</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30870</t>
+          <t>30581</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57664</t>
+          <t>58794</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -6084,12 +6084,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>562283</t>
+          <t>561678</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>578740</t>
+          <t>578810</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6119,12 +6119,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>714900</t>
+          <t>713987</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>745027</t>
+          <t>744826</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6134,12 +6134,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6154,12 +6154,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1285246</t>
+          <t>1285667</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1318478</t>
+          <t>1318480</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>3677</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3634</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -6652,7 +6652,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>656</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>4594</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6722,32 +6722,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>609</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>5768</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -6765,32 +6765,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>642</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6470</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6800,32 +6800,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>8425</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2258</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12963</t>
+          <t>13888</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6835,32 +6835,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>9132</t>
+          <t>10611</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>6804</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15217</t>
+          <t>17443</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -6878,32 +6878,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>365372</t>
+          <t>404238</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>361145</t>
+          <t>400238</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>367496</t>
+          <t>406144</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6913,32 +6913,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>598801</t>
+          <t>428021</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>591629</t>
+          <t>422151</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>604934</t>
+          <t>431798</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6948,32 +6948,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>964174</t>
+          <t>832259</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>957567</t>
+          <t>825376</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>970572</t>
+          <t>836901</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -6991,17 +6991,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7026,17 +7026,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7061,17 +7061,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>976124</t>
+          <t>845814</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>976124</t>
+          <t>845814</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>976124</t>
+          <t>845814</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7108,32 +7108,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>688</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5023</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7143,32 +7143,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10181</t>
+          <t>10993</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6373</t>
+          <t>6487</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15644</t>
+          <t>16521</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7178,32 +7178,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>12328</t>
+          <t>13107</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8090</t>
+          <t>8502</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18684</t>
+          <t>19422</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -7221,32 +7221,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>3178</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>949</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>8055</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7256,32 +7256,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6902</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3246</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11526</t>
+          <t>12090</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7291,32 +7291,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>8611</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5098</t>
+          <t>5815</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14679</t>
+          <t>15683</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -7334,32 +7334,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10465</t>
+          <t>11155</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6423</t>
+          <t>6943</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17555</t>
+          <t>18143</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7369,67 +7369,67 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31169</t>
+          <t>32982</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24283</t>
+          <t>24889</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39986</t>
+          <t>41817</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>5,36%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>9,01%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>44138</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>35288</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>54937</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>5,71%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>9,4%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>41634</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>33184</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>51569</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>5,89%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -7447,27 +7447,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>266464</t>
+          <t>292363</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>258718</t>
+          <t>284421</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>271449</t>
+          <t>297774</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -7482,32 +7482,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>377937</t>
+          <t>413387</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>367973</t>
+          <t>402286</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>387213</t>
+          <t>423240</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7517,32 +7517,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>644401</t>
+          <t>705750</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>631727</t>
+          <t>691942</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>655004</t>
+          <t>716404</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,67%</t>
         </is>
       </c>
     </row>
@@ -7560,17 +7560,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>281491</t>
+          <t>308810</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>281491</t>
+          <t>308810</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>281491</t>
+          <t>308810</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7595,17 +7595,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>425483</t>
+          <t>464264</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>425483</t>
+          <t>464264</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>425483</t>
+          <t>464264</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7630,17 +7630,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>706974</t>
+          <t>773074</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>706974</t>
+          <t>773074</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>706974</t>
+          <t>773074</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7677,7 +7677,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -7687,22 +7687,22 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7712,32 +7712,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>11149</t>
+          <t>11995</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5466</t>
+          <t>7603</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17106</t>
+          <t>17415</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7747,32 +7747,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>13296</t>
+          <t>14108</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7778</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19647</t>
+          <t>20853</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -7790,32 +7790,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>3834</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>1584</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7787</t>
+          <t>8990</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7825,32 +7825,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7383</t>
+          <t>8188</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2902</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12392</t>
+          <t>13224</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7860,32 +7860,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>10461</t>
+          <t>12022</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>7442</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>16650</t>
+          <t>18864</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -7903,32 +7903,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>12594</t>
+          <t>13341</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7693</t>
+          <t>8186</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20457</t>
+          <t>20952</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7938,32 +7938,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>38171</t>
+          <t>41408</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18403</t>
+          <t>32316</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51716</t>
+          <t>50530</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7973,32 +7973,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>50765</t>
+          <t>54749</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33128</t>
+          <t>44984</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64629</t>
+          <t>66795</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -8016,22 +8016,22 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>631836</t>
+          <t>696602</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>624285</t>
+          <t>687906</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>637493</t>
+          <t>702606</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8051,32 +8051,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>976739</t>
+          <t>841408</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>958218</t>
+          <t>831017</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1004838</t>
+          <t>852541</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8086,32 +8086,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1608575</t>
+          <t>1538009</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1593038</t>
+          <t>1522743</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1635876</t>
+          <t>1549634</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -8129,17 +8129,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>649656</t>
+          <t>715890</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>649656</t>
+          <t>715890</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>649656</t>
+          <t>715890</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8164,17 +8164,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1033442</t>
+          <t>902998</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1033442</t>
+          <t>902998</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1033442</t>
+          <t>902998</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8199,17 +8199,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1683098</t>
+          <t>1618888</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1683098</t>
+          <t>1618888</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1683098</t>
+          <t>1618888</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
